--- a/public/reportes/Reporte de inventario.xlsx
+++ b/public/reportes/Reporte de inventario.xlsx
@@ -16,6 +16,9 @@
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="19">
+  <si>
+    <t>Clasificación</t>
+  </si>
   <si>
     <t>Producto</t>
   </si>
@@ -56,22 +59,19 @@
     <t>Abastecimiento de producto</t>
   </si>
   <si>
-    <t>25/03/2026</t>
-  </si>
-  <si>
-    <t>Agua purificada 1 L.</t>
-  </si>
-  <si>
-    <t>27/03/2026</t>
-  </si>
-  <si>
-    <t>Rufles de queso 30 gr.</t>
-  </si>
-  <si>
     <t>Prueba - Pedro</t>
   </si>
   <si>
     <t>11/05/2026</t>
+  </si>
+  <si>
+    <t>Insumo</t>
+  </si>
+  <si>
+    <t>Crema para masaje 500 gr.</t>
+  </si>
+  <si>
+    <t>18/05/2026</t>
   </si>
 </sst>
 </file>
@@ -443,16 +443,17 @@
   <dimension ref="A1:Z1000"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="50" customWidth="true" style="0"/>
-    <col min="2" max="2" width="25" customWidth="true" style="0"/>
-    <col min="3" max="3" width="35" customWidth="true" style="0"/>
+    <col min="1" max="1" width="15" customWidth="true" style="0"/>
+    <col min="2" max="2" width="50" customWidth="true" style="0"/>
+    <col min="3" max="3" width="25" customWidth="true" style="0"/>
     <col min="4" max="4" width="35" customWidth="true" style="0"/>
-    <col min="5" max="5" width="15" customWidth="true" style="0"/>
-    <col min="6" max="6" width="20" customWidth="true" style="0"/>
-    <col min="7" max="7" width="15" customWidth="true" style="0"/>
-    <col min="8" max="8" width="25" customWidth="true" style="0"/>
+    <col min="5" max="5" width="35" customWidth="true" style="0"/>
+    <col min="6" max="6" width="15" customWidth="true" style="0"/>
+    <col min="7" max="7" width="20" customWidth="true" style="0"/>
+    <col min="8" max="8" width="15" customWidth="true" style="0"/>
     <col min="9" max="9" width="25" customWidth="true" style="0"/>
-    <col min="10" max="10" width="50" customWidth="true" style="0"/>
+    <col min="10" max="10" width="25" customWidth="true" style="0"/>
+    <col min="11" max="11" width="50" customWidth="true" style="0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26">
@@ -471,10 +472,10 @@
       <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
       <c r="H1" s="3" t="s">
@@ -486,7 +487,9 @@
       <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1"/>
+      <c r="K1" s="3" t="s">
+        <v>10</v>
+      </c>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
@@ -505,7 +508,7 @@
     </row>
     <row r="2" spans="1:26">
       <c r="A2" s="1" t="s">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>11</v>
@@ -513,19 +516,23 @@
       <c r="C2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1">
-        <v>25</v>
-      </c>
-      <c r="F2" s="2">
-        <v>425.0</v>
-      </c>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="J2" s="1"/>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1">
+        <v>5</v>
+      </c>
+      <c r="G2" s="2">
+        <v>100.0</v>
+      </c>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
@@ -545,27 +552,29 @@
     </row>
     <row r="3" spans="1:26">
       <c r="A3" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1">
-        <v>25</v>
+      <c r="D3" s="1" t="s">
+        <v>13</v>
       </c>
-      <c r="F3" s="2">
-        <v>325.0</v>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1">
+        <v>100</v>
       </c>
-      <c r="G3" s="1"/>
+      <c r="G3" s="2">
+        <v>2000.0</v>
+      </c>
       <c r="H3" s="1"/>
-      <c r="I3" s="1" t="s">
-        <v>15</v>
+      <c r="I3" s="1"/>
+      <c r="J3" s="1" t="s">
+        <v>18</v>
       </c>
-      <c r="J3" s="1"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
@@ -584,27 +593,15 @@
       <c r="Z3" s="1"/>
     </row>
     <row r="4" spans="1:26">
-      <c r="A4" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>12</v>
-      </c>
+      <c r="A4" s="1"/>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
       <c r="D4" s="1"/>
-      <c r="E4" s="1">
-        <v>25</v>
-      </c>
-      <c r="F4" s="2">
-        <v>475.0</v>
-      </c>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
-      <c r="I4" s="1" t="s">
-        <v>15</v>
-      </c>
+      <c r="I4" s="1"/>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
       <c r="L4" s="1"/>
@@ -624,29 +621,15 @@
       <c r="Z4" s="1"/>
     </row>
     <row r="5" spans="1:26">
-      <c r="A5" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E5" s="1">
-        <v>5</v>
-      </c>
-      <c r="F5" s="2">
-        <v>100.0</v>
-      </c>
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
-      <c r="I5" s="1" t="s">
-        <v>18</v>
-      </c>
+      <c r="I5" s="1"/>
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
       <c r="L5" s="1"/>
